--- a/out/LSTM-mamba2_repeat_4_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-7.712256331345998e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.889109252280405</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
-        <v>-6.306551084644161e-05</v>
+        <v>1.779592907008404</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.0813223436080609</v>
+        <v>0.1333258984963202</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.0813854091189074</v>
+        <v>1.155942144807108</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.1667007545622656</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.08144265640502645</v>
+        <v>1.356038928517799</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.09557022842620413</v>
+        <v>0.2389645784281521</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.109927583166712</v>
+        <v>1.667361733030028</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1314842010658518</v>
+        <v>0.2556451129256772</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2773370801690046</v>
+        <v>1.939704871897068</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1537115489597954</v>
+        <v>0.2709315542955592</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4532886487171303</v>
+        <v>2.225943688836998</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.06874208748906993</v>
+        <v>0.1222670373213373</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4369227351116413</v>
+        <v>2.19931958941948</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03308993527229902</v>
+        <v>0.05904874746033055</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4343015391427779</v>
+        <v>2.19505546025556</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01569089532132553</v>
+        <v>0.02813558306727647</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4325645086269432</v>
+        <v>2.192229698691393</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.00431927324799718</v>
+        <v>0.008333563627179606</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4254960567390518</v>
+        <v>2.180734450292196</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002984402638138277</v>
+        <v>0.005510641582937633</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4271442962935483</v>
+        <v>2.18341892269172</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001530180290689339</v>
+        <v>0.002817967231921131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4272173897525841</v>
+        <v>2.183540957973626</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.000782617737006901</v>
+        <v>0.001439560167255453</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4272514124201178</v>
+        <v>2.183599447234295</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000278657114361179</v>
+        <v>0.0005376864856202011</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4270254362510392</v>
+        <v>2.183234922977324</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001514935836916001</v>
+        <v>0.0002911771458358382</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4270502921990207</v>
+        <v>2.183278531161338</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>6.991642890876991e-05</v>
+        <v>0.0001372566611499408</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.427038486393264</v>
+        <v>2.183262475273386</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.286559863260411e-05</v>
+        <v>8.355596056915365e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4270544497354924</v>
+        <v>2.183291468911106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.063953424346452e-05</v>
+        <v>4.132161208684532e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4270519609073287</v>
+        <v>2.183290504722986</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.395902747928427e-06</v>
+        <v>1.698004887727391e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4270460951343845</v>
+        <v>2.183284113910244</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.158324102806951e-06</v>
+        <v>9.070610155389825e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4270450097222657</v>
+        <v>2.1832855457952</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.844180684889389e-06</v>
+        <v>1.993667665820105e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4270392097731743</v>
+        <v>2.18327917324003</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.168604696895391e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4270336616449533</v>
+        <v>2.183273351047698</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4270288270106348</v>
+        <v>2.183268599772485</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4270286830267273</v>
+        <v>2.183263310624922</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4270286602924259</v>
+        <v>2.183263287890621</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4270289785726427</v>
+        <v>2.183263606170838</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4270300698190995</v>
+        <v>2.183264697417295</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4270293802119636</v>
+        <v>2.183264007810159</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4270294105243653</v>
+        <v>2.183264038122561</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4270292210718551</v>
+        <v>2.18326384867005</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.427029274118558</v>
+        <v>2.183263901716753</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4270293271652609</v>
+        <v>2.183263954763456</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4270292892747589</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4270291604470522</v>
+        <v>2.183263788045247</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4270290164631447</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4270288573230363</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4270289103697392</v>
+        <v>2.183263537967934</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4270288573230363</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4270288573230363</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4270286754486268</v>
+        <v>2.183263303046822</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4270288421668355</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4270290391974458</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4270288800573375</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4270289179478395</v>
+        <v>2.183263545546035</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4270291149784496</v>
+        <v>2.183263742576645</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4270290922441485</v>
+        <v>2.183263719842344</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4270289406821406</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4270288649011366</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4270289634164418</v>
+        <v>2.183263591014637</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4270289709945421</v>
+        <v>2.183263598592738</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.427029236228056</v>
+        <v>2.183263863826252</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4270289406821406</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4270291831813534</v>
+        <v>2.183263810779549</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4270292665404578</v>
+        <v>2.183263894138653</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.427029099822249</v>
+        <v>2.183263727420444</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4270292892747589</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4270289406821406</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4270287360734299</v>
+        <v>2.183263363671625</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.427028849744936</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4270288649011366</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4270286299800244</v>
+        <v>2.18326325757822</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4270286906048276</v>
+        <v>2.183263318203023</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4270285617771209</v>
+        <v>2.183263189375316</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4270286981829279</v>
+        <v>2.183263325781123</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4270288724792372</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4270290164631447</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.427028849744936</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4270288421668355</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4270285541990204</v>
+        <v>2.183263181797216</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4270285693552212</v>
+        <v>2.183263196953417</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4270287966982331</v>
+        <v>2.183263424296428</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4270287815420323</v>
+        <v>2.183263409140228</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4270288876354378</v>
+        <v>2.183263515233633</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4270286148238235</v>
+        <v>2.183263242422019</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4270287133391288</v>
+        <v>2.183263340937324</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4270288649011366</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4270288800573375</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4270288573230363</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4270289406821406</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4270290391974458</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4270288724792372</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4270288573230363</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4270288270106348</v>
+        <v>2.18326345460883</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.427028811854434</v>
+        <v>2.183263439452629</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.427028849744936</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4270288649011366</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4270288573230363</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_4_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270782</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.414642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270782</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817695</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-3.717576504230965e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.4285816658537211</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC40" t="n">
-        <v>-6.306551084644161e-05</v>
+        <v>0.8578258416172562</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.0813223436080609</v>
+        <v>0.06426770991105465</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.0813854091189074</v>
+        <v>0.5572044254633207</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.08035554874927242</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.08144265640502645</v>
+        <v>0.6536580874142437</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.09557022842620413</v>
+        <v>0.1151894607287152</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.109927583166712</v>
+        <v>0.8037266948978949</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1314842010658518</v>
+        <v>0.1232299062761035</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2773370801690046</v>
+        <v>0.9350056350405224</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1537115489597954</v>
+        <v>0.1305988625146826</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4532886487171303</v>
+        <v>1.072982778599518</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.06874208748906993</v>
+        <v>0.05893683767405979</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4369227351116413</v>
+        <v>1.060149064297075</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03308993527229902</v>
+        <v>0.02846379879756442</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4343015391427779</v>
+        <v>1.05809360968407</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01569089532132553</v>
+        <v>0.01356127109459593</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4325645086269432</v>
+        <v>1.056730630484486</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.00431927324799718</v>
+        <v>0.004014600382150364</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4254960567390518</v>
+        <v>1.05118700315014</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002984402638138277</v>
+        <v>0.002653812237435603</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4271442962935483</v>
+        <v>1.052478348717461</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001530180290689339</v>
+        <v>0.001355809927412661</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4272173897525841</v>
+        <v>1.052534575051841</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.000782617737006901</v>
+        <v>0.0006906035369850299</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4272514124201178</v>
+        <v>1.052560169966715</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000278657114361179</v>
+        <v>0.0002568821813453133</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4270254362510392</v>
+        <v>1.052381796373742</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001514935836916001</v>
+        <v>0.0001377260340657382</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4270502921990207</v>
+        <v>1.052400220373281</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>6.991642890876991e-05</v>
+        <v>6.334677574801625e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.427038486393264</v>
+        <v>1.052389892856983</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.286559863260411e-05</v>
+        <v>3.731007004970674e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4270544497354924</v>
+        <v>1.052401323714182</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.063953424346452e-05</v>
+        <v>1.764612146467993e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4270519609073287</v>
+        <v>1.052398296777768</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.395902747928427e-06</v>
+        <v>5.990024438636956e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4270460951343845</v>
+        <v>1.052392616527597</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.158324102806951e-06</v>
+        <v>1.395731888813558e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4270450097222657</v>
+        <v>1.052390693051513</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.844180684889389e-06</v>
+        <v>-1.503166167089948e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4270392097731743</v>
+        <v>1.052385006773928</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.168604696895391e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4270336616449533</v>
+        <v>1.05237959630401</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4270288270106348</v>
+        <v>1.052374761669692</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4270286830267273</v>
+        <v>1.052374617685784</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4270286602924259</v>
+        <v>1.052374594951483</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4270289785726427</v>
+        <v>1.0523749132317</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4270300698190995</v>
+        <v>1.052376004478156</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4270293802119636</v>
+        <v>1.05237531487102</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823052</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4270294105243653</v>
+        <v>1.052375345183422</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.6238367016906172</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4270292210718551</v>
+        <v>1.052375155730912</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.427029274118558</v>
+        <v>1.052375208777615</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4270293271652609</v>
+        <v>1.052375261824318</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4270292892747589</v>
+        <v>1.052375223933816</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4270291604470522</v>
+        <v>1.052375095106109</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4270290164631447</v>
+        <v>1.052374951122202</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4270288573230363</v>
+        <v>1.052374791982093</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4270289103697392</v>
+        <v>1.052374845028796</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4270288573230363</v>
+        <v>1.052374791982093</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4270288573230363</v>
+        <v>1.052374791982093</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4270286754486268</v>
+        <v>1.052374610107684</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4270288421668355</v>
+        <v>1.052374776825892</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4270290391974458</v>
+        <v>1.052374973856503</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4270288800573375</v>
+        <v>1.052374814716394</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4270289179478395</v>
+        <v>1.052374852606896</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4270291149784496</v>
+        <v>1.052375049637506</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4270290922441485</v>
+        <v>1.052375026903205</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4270289406821406</v>
+        <v>1.052374875341197</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4270288649011366</v>
+        <v>1.052374799560194</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4270289634164418</v>
+        <v>1.052374898075499</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4270289709945421</v>
+        <v>1.052374905653599</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.427029236228056</v>
+        <v>1.052375170887113</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4270289406821406</v>
+        <v>1.052374875341197</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4270291831813534</v>
+        <v>1.05237511784041</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4270292665404578</v>
+        <v>1.052375201199515</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.427029099822249</v>
+        <v>1.052375034481306</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4270292892747589</v>
+        <v>1.052375223933816</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4270289406821406</v>
+        <v>1.052374875341197</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4270287360734299</v>
+        <v>1.052374670732487</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.427028849744936</v>
+        <v>1.052374784403993</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4270288649011366</v>
+        <v>1.052374799560194</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4270286299800244</v>
+        <v>1.052374564639081</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4270286906048276</v>
+        <v>1.052374625263884</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4270285617771209</v>
+        <v>1.052374496436178</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4270286981829279</v>
+        <v>1.052374632841985</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4270288724792372</v>
+        <v>1.052374807138294</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4270290164631447</v>
+        <v>1.052374951122202</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.427028849744936</v>
+        <v>1.052374784403993</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906173</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4270288421668355</v>
+        <v>1.052374776825892</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4270285541990204</v>
+        <v>1.052374488858077</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4270285693552212</v>
+        <v>1.052374504014278</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4270287966982331</v>
+        <v>1.05237473135729</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4270287815420323</v>
+        <v>1.052374716201089</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4270288876354378</v>
+        <v>1.052374822294495</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4270286148238235</v>
+        <v>1.05237454948288</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4270287133391288</v>
+        <v>1.052374647998186</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4270288649011366</v>
+        <v>1.052374799560194</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4270288800573375</v>
+        <v>1.052374814716394</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4270288573230363</v>
+        <v>1.052374791982093</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.4825578011270782</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4270289406821406</v>
+        <v>1.052374875341197</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270782</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4270290391974458</v>
+        <v>1.052374973856503</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4270288724792372</v>
+        <v>1.052374807138294</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4270288573230363</v>
+        <v>1.052374791982093</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4270288270106348</v>
+        <v>1.052374761669692</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.427028811854434</v>
+        <v>1.052374746513491</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.427028849744936</v>
+        <v>1.052374784403993</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270783</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4270288649011366</v>
+        <v>1.052374799560194</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.1559591754226544</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4270288573230363</v>
+        <v>1.052374791982093</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_4_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2469930499792099</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1012951582670212</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1706394502817695</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.005854422226548195</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4825578011270782</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0367618016898632</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.05668941140174866</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.05563430488109589</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.04559140279889107</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.03386179357767105</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.02748807519674301</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.335755052535926</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.02189406007528305</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.335755052535926</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.02023766189813614</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01954405382275581</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01827149838209152</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01672504469752312</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01873946748673916</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.02308230474591255</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.135755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.02471058815717697</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.135755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.02235051803290844</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.135755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0205084104090929</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.135755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.02086089365184307</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.135755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01698596030473709</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.135755052535926</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01185022294521332</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.007851330563426018</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01115436106920242</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01295131631195545</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01347861625254154</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01417330093681812</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01522685587406158</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.135755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01324129104614258</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.135755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01606543362140656</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.135755052535926</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0184972807765007</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.135755052535926</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01863332465291023</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02018308266997337</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01925433613359928</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01519080623984337</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4825578011270782</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.001024600118398666</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1706394502817695</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.008939886465668678</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.009178411215543747</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-3.717576504230965e-05</v>
+        <v>-2.374188724905252e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.4285816658537211</v>
+        <v>0.2737088198054883</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.01745201647281647</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>0.8578258416172562</v>
+        <v>0.5478408956059538</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.06426770991105465</v>
+        <v>0.04104385848346254</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0180177241563797</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.5572044254633207</v>
+        <v>0.3558523317891599</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.08035554874927242</v>
+        <v>0.05131817791221478</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.01897629164159298</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.6536580874142437</v>
+        <v>0.4174514153839927</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1151894607287152</v>
+        <v>0.07356452734066871</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.02861226536333561</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.8037266948978949</v>
+        <v>0.5132911398550274</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1232299062761035</v>
+        <v>0.07869912454886685</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.03969704359769821</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.9350056350405224</v>
+        <v>0.5971310431035201</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1305988625146826</v>
+        <v>0.08340520947857311</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.04762175679206848</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.072982778599518</v>
+        <v>0.6852490732180814</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.05893683767405979</v>
+        <v>0.03763988566566401</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0382867194712162</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.060149064297075</v>
+        <v>0.6770528489537041</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02846379879756442</v>
+        <v>0.01817834438752623</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0702245682477951</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.05809360968407</v>
+        <v>0.675740137249484</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01356127109459593</v>
+        <v>0.008659070097109081</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.09148123860359192</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.056730630484486</v>
+        <v>0.6748678667302993</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004014600382150364</v>
+        <v>0.002562109210075422</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.1036302149295807</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.05118700315014</v>
+        <v>0.6713256341973552</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002653812237435603</v>
+        <v>0.001692564140025768</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.1049951761960983</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.052478348717461</v>
+        <v>0.6721485431140889</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001355809927412661</v>
+        <v>0.0008638323686951406</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.1030518859624863</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.052534575051841</v>
+        <v>0.6721826568485764</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0006906035369850299</v>
+        <v>0.0004399446647574287</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.09533213078975677</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.052560169966715</v>
+        <v>0.6721972124257304</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002568821813453133</v>
+        <v>0.00016227156669744</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.08213227987289429</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.052381796373742</v>
+        <v>0.6720814738013171</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001377260340657382</v>
+        <v>8.575065749844627e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.06683659553527832</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.052400220373281</v>
+        <v>0.6720914358767597</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>6.334677574801625e-05</v>
+        <v>3.871014728070806e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.05327960103750229</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.052389892856983</v>
+        <v>0.6720830178176805</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.731007004970674e-05</v>
+        <v>2.255074328818113e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.04932394996285439</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.052401323714182</v>
+        <v>0.6720885936160828</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.764612146467993e-05</v>
+        <v>9.411168204796322e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.037948127835989</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.052398296777768</v>
+        <v>0.6720848492020007</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.990024438636956e-06</v>
+        <v>1.993651915496244e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.05692425742745399</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.052392616527597</v>
+        <v>0.6720794163155286</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.395731888813558e-06</v>
+        <v>-1.162560866711865e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.05510560423135757</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.052390693051513</v>
+        <v>0.6720763743857638</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.503166167089948e-06</v>
+        <v>-2.668777444726632e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.05948084592819214</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.052385006773928</v>
+        <v>0.6720709168673735</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.05959083884954453</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.05237959630401</v>
+        <v>0.6720656428032632</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.06509791314601898</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.052374761669692</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.06354844570159912</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.052374617685784</v>
+        <v>0.67206558217846</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.05756933614611626</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.052374594951483</v>
+        <v>0.6720655594441586</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.05668579041957855</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.0523749132317</v>
+        <v>0.6720658777243753</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.03155545890331268</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.052376004478156</v>
+        <v>0.6720669689708322</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01550231501460075</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6825578011270783</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.05237531487102</v>
+        <v>0.6720662793636962</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.061942208558321</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.02936054971823052</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.052375345183422</v>
+        <v>0.6720663096760979</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.1244784891605377</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6238367016906172</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.052375155730912</v>
+        <v>0.6720661202235878</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.1609917879104614</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.052375208777615</v>
+        <v>0.6720661732702907</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.1742070764303207</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.052375261824318</v>
+        <v>0.6720662263169936</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.1619985103607178</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.052375223933816</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.1403877139091492</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.052375095106109</v>
+        <v>0.6720660595987848</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.1162675470113754</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.052374951122202</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.09184275567531586</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.052374791982093</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.07287433743476868</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.052374845028796</v>
+        <v>0.6720658095214719</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.05400825664401054</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.052374791982093</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.04511618986725807</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.052374791982093</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0382174588739872</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.052374610107684</v>
+        <v>0.6720655746003594</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.03579651936888695</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.052374776825892</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.03350234031677246</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.052374973856503</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.02238037995994091</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.052374814716394</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.02469540014863014</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.052374852606896</v>
+        <v>0.6720658170995721</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.03662542253732681</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.052375049637506</v>
+        <v>0.6720660141301823</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.03456677496433258</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.052375026903205</v>
+        <v>0.6720659913958812</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.02611427195370197</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.052374875341197</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.02304649353027344</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.052374799560194</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.02581094577908516</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.052374898075499</v>
+        <v>0.6720658625681745</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.03401025757193565</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.052374905653599</v>
+        <v>0.6720658701462748</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.03559746965765953</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.052375170887113</v>
+        <v>0.6720661353797887</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02783802151679993</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.052374875341197</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.03409634903073311</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.05237511784041</v>
+        <v>0.6720660823330861</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.03544726222753525</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.052375201199515</v>
+        <v>0.6720661656921904</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.04517687484622002</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.052375034481306</v>
+        <v>0.6720659989739817</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.04573793709278107</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.052375223933816</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.04569604247808456</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.052374875341197</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.04031133279204369</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8238367016906173</v>
+        <v>-0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.052374670732487</v>
+        <v>0.6720656352251626</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.03710850700736046</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.052374784403993</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.04171090945601463</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.052374799560194</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.03519086539745331</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.052374564639081</v>
+        <v>0.6720655291317571</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02379058673977852</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.052374625263884</v>
+        <v>0.6720655897565603</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01111503411084414</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.052374496436178</v>
+        <v>0.6720654609288536</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.02342097461223602</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.052374632841985</v>
+        <v>0.6720655973346605</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01828393340110779</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.052374807138294</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01573842018842697</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.052374951122202</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01277730334550142</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.052374784403993</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01540389284491539</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8238367016906173</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.052374776825892</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.003060819581151009</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.052374488858077</v>
+        <v>0.6720654533507531</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.005353646352887154</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.052374504014278</v>
+        <v>0.6720654685069539</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.002095811069011688</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6825578011270783</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.05237473135729</v>
+        <v>0.6720656958499658</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.001916805282235146</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.6825578011270783</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.052374716201089</v>
+        <v>0.6720656806937649</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.0003696419298648834</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.6825578011270783</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.052374822294495</v>
+        <v>0.6720657867871704</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.007465293630957603</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.05237454948288</v>
+        <v>0.6720655139755563</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.008546915836632252</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.052374647998186</v>
+        <v>0.6720656124908615</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.004864889197051525</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.052374799560194</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.004001246765255928</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.052374814716394</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.002971641719341278</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.6825578011270783</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.052374791982093</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.0001062098890542984</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4825578011270782</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.052374875341197</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.002911785617470741</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.4825578011270782</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.052374973856503</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.004965082742273808</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.135755052535926</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.052374807138294</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.006964400410652161</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.335755052535926</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.052374791982093</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.005304131656885147</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.335755052535926</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.052374761669692</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.005988657474517822</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.052374746513491</v>
+        <v>0.6720657110061666</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.005766432732343674</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.052374784403993</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001403547823429108</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6825578011270783</v>
+        <v>-0.09000000000000052</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.052374799560194</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.00668913871049881</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.1559591754226544</v>
+        <v>-0.3000000000000006</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.052374791982093</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
   </sheetData>
